--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1495" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18AD047D-2409-4AAF-B519-D7232AE394C2}"/>
+  <xr:revisionPtr revIDLastSave="1502" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB9AFC5-B4BB-4928-A1CF-E1FB4EE48B92}"/>
   <bookViews>
-    <workbookView xWindow="13776" yWindow="720" windowWidth="8964" windowHeight="10764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="420" windowWidth="8196" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Net</t>
+  </si>
+  <si>
+    <t>Div-Exp</t>
   </si>
 </sst>
 </file>
@@ -117,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -132,6 +135,7 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -147,6 +151,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -3517,6 +3525,56 @@
         <v>-262000</v>
       </c>
     </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="4">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B206" s="6">
+        <v>-266000</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B207" s="7">
+        <v>273000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B208" s="6">
+        <v>238000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B209" s="8">
+        <f>B206+B207-B208</f>
+        <v>-231000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" s="10">
+        <f>B207-B208</f>
+        <v>35000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1502" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB9AFC5-B4BB-4928-A1CF-E1FB4EE48B92}"/>
+  <xr:revisionPtr revIDLastSave="1509" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1094CAD-C36A-4263-93DD-AB75D5E3BD27}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="420" windowWidth="8196" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13968" yWindow="744" windowWidth="7812" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -3532,6 +3532,9 @@
       <c r="B205" s="4">
         <v>46265</v>
       </c>
+      <c r="C205" s="4">
+        <v>46297</v>
+      </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
@@ -3540,6 +3543,9 @@
       <c r="B206" s="6">
         <v>-266000</v>
       </c>
+      <c r="C206" s="6">
+        <v>-209000</v>
+      </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
@@ -3548,6 +3554,9 @@
       <c r="B207" s="7">
         <v>273000</v>
       </c>
+      <c r="C207" s="7">
+        <v>377000</v>
+      </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
@@ -3556,8 +3565,11 @@
       <c r="B208" s="6">
         <v>238000</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C208" s="6">
+        <v>248000</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>4</v>
       </c>
@@ -3565,14 +3577,22 @@
         <f>B206+B207-B208</f>
         <v>-231000</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C209" s="8">
+        <f>C206+C207-C208</f>
+        <v>-80000</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B210" s="10">
         <f>B207-B208</f>
         <v>35000</v>
+      </c>
+      <c r="C210" s="10">
+        <f>C207-C208</f>
+        <v>129000</v>
       </c>
     </row>
   </sheetData>
